--- a/diseases/d091/1990-1994.xlsx
+++ b/diseases/d091/1990-1994.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>1</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1158,9 +1155,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="S4" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1551,9 +1545,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="S6" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1944,9 +1935,6 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="S8" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2337,9 +2325,6 @@
       <c r="O10" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="S10" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2730,9 +2715,6 @@
       <c r="O12" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="S12" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3123,9 +3105,6 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="S14" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3516,9 +3495,6 @@
       <c r="O16" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="S16" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3909,9 +3885,6 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="S18" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4302,9 +4275,6 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="S20" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4695,9 +4665,6 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="S22" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5088,9 +5055,6 @@
       <c r="O24" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="S24" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5481,9 +5445,6 @@
       <c r="O26" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="S26" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5874,9 +5835,6 @@
       <c r="O28" t="n">
         <v>0</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="S28" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6267,9 +6225,6 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="S30" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6660,9 +6615,6 @@
       <c r="O32" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="S32" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7053,9 +7005,6 @@
       <c r="O34" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="S34" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7446,9 +7395,6 @@
       <c r="O36" t="n">
         <v>0</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="S36" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7839,9 +7785,6 @@
       <c r="O38" t="n">
         <v>0</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="S38" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8232,9 +8175,6 @@
       <c r="O40" t="n">
         <v>0</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="S40" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8625,9 +8565,6 @@
       <c r="O42" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="S42" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9018,9 +8955,6 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="S44" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9411,9 +9345,6 @@
       <c r="O46" t="n">
         <v>0</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="S46" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9804,9 +9735,6 @@
       <c r="O48" t="n">
         <v>2</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="S48" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10197,9 +10125,6 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="S50" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10590,9 +10515,6 @@
       <c r="O52" t="n">
         <v>1</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="S52" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10983,9 +10905,6 @@
       <c r="O54" t="n">
         <v>0</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="S54" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11376,9 +11295,6 @@
       <c r="O56" t="n">
         <v>0</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="S56" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11769,9 +11685,6 @@
       <c r="O58" t="n">
         <v>0</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="S58" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12162,9 +12075,6 @@
       <c r="O60" t="n">
         <v>0</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="S60" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12555,9 +12465,6 @@
       <c r="O62" t="n">
         <v>0</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="S62" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12948,9 +12855,6 @@
       <c r="O64" t="n">
         <v>0</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="S64" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -13341,9 +13245,6 @@
       <c r="O66" t="n">
         <v>0</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="S66" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -13734,9 +13635,6 @@
       <c r="O68" t="n">
         <v>0</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="S68" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14127,9 +14025,6 @@
       <c r="O70" t="n">
         <v>0</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="S70" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14518,9 +14413,6 @@
         <v>0</v>
       </c>
       <c r="O72" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q72" t="n">
         <v>0</v>
       </c>
       <c r="S72" t="inlineStr">

--- a/diseases/d091/1990-1994.xlsx
+++ b/diseases/d091/1990-1994.xlsx
@@ -721,12 +721,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -772,12 +772,12 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D13_ANNUAL</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D13_ANNUAL</t>
         </is>
       </c>
       <c r="AT2" t="n">
@@ -810,42 +810,42 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -916,29 +916,29 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D13_ANNUAL</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D13_ANNUAL</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_CA_PHAC_CNDSS</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Botulisme</t>
+          <t>Botulism</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -948,12 +948,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:CA:national</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -998,17 +998,17 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D13_ANNUAL</t>
         </is>
       </c>
       <c r="AT3" t="n">
@@ -1044,42 +1044,42 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -1141,19 +1141,19 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1990-02-01</t>
+          <t>1990-01-01</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>1990-02</t>
+          <t>1990-01</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1185,17 +1185,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS4" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
@@ -1297,19 +1302,19 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1990-02-01</t>
+          <t>1990-01-01</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>1990-02</t>
+          <t>1990-01</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1411,7 +1416,7 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -1419,17 +1424,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS5" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
@@ -1531,12 +1541,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1990-03-01</t>
+          <t>1990-02-01</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>1990-03</t>
+          <t>1990-02</t>
         </is>
       </c>
       <c r="N6" t="n">
@@ -1567,7 +1577,7 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -1575,17 +1585,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS6" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
@@ -1687,12 +1702,12 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1990-03-01</t>
+          <t>1990-02-01</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>1990-03</t>
+          <t>1990-02</t>
         </is>
       </c>
       <c r="N7" t="n">
@@ -1801,7 +1816,7 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -1809,17 +1824,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS7" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
@@ -1921,12 +1941,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>1990-04-01</t>
+          <t>1990-03-01</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>1990-04</t>
+          <t>1990-03</t>
         </is>
       </c>
       <c r="N8" t="n">
@@ -1957,7 +1977,7 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -1965,17 +1985,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS8" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
@@ -2077,12 +2102,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1990-04-01</t>
+          <t>1990-03-01</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>1990-04</t>
+          <t>1990-03</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -2191,7 +2216,7 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -2199,17 +2224,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS9" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
@@ -2311,12 +2341,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1990-05-01</t>
+          <t>1990-04-01</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1990-05</t>
+          <t>1990-04</t>
         </is>
       </c>
       <c r="N10" t="n">
@@ -2347,7 +2377,7 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -2355,17 +2385,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS10" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
@@ -2467,12 +2502,12 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1990-05-01</t>
+          <t>1990-04-01</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1990-05</t>
+          <t>1990-04</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -2581,7 +2616,7 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -2589,17 +2624,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS11" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
@@ -2701,12 +2741,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1990-06-01</t>
+          <t>1990-05-01</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1990-06</t>
+          <t>1990-05</t>
         </is>
       </c>
       <c r="N12" t="n">
@@ -2737,7 +2777,7 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
@@ -2745,17 +2785,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS12" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
@@ -2857,12 +2902,12 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1990-06-01</t>
+          <t>1990-05-01</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1990-06</t>
+          <t>1990-05</t>
         </is>
       </c>
       <c r="N13" t="n">
@@ -2971,7 +3016,7 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
@@ -2979,17 +3024,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS13" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
@@ -3091,12 +3141,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1990-07-01</t>
+          <t>1990-06-01</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>1990-07</t>
+          <t>1990-06</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -3127,7 +3177,7 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
@@ -3135,17 +3185,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS14" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
@@ -3247,12 +3302,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1990-07-01</t>
+          <t>1990-06-01</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>1990-07</t>
+          <t>1990-06</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -3361,7 +3416,7 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
@@ -3369,17 +3424,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS15" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
@@ -3481,12 +3541,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1990-08-01</t>
+          <t>1990-07-01</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1990-08</t>
+          <t>1990-07</t>
         </is>
       </c>
       <c r="N16" t="n">
@@ -3517,7 +3577,7 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
@@ -3525,17 +3585,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS16" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
@@ -3637,12 +3702,12 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1990-08-01</t>
+          <t>1990-07-01</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>1990-08</t>
+          <t>1990-07</t>
         </is>
       </c>
       <c r="N17" t="n">
@@ -3751,7 +3816,7 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
@@ -3759,17 +3824,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS17" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
@@ -3871,12 +3941,12 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>1990-09-01</t>
+          <t>1990-08-01</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>1990-09</t>
+          <t>1990-08</t>
         </is>
       </c>
       <c r="N18" t="n">
@@ -3907,7 +3977,7 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
@@ -3915,17 +3985,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS18" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
@@ -4027,12 +4102,12 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1990-09-01</t>
+          <t>1990-08-01</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>1990-09</t>
+          <t>1990-08</t>
         </is>
       </c>
       <c r="N19" t="n">
@@ -4141,7 +4216,7 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
@@ -4149,17 +4224,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS19" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
@@ -4261,12 +4341,12 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1990-10-01</t>
+          <t>1990-09-01</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1990-10</t>
+          <t>1990-09</t>
         </is>
       </c>
       <c r="N20" t="n">
@@ -4297,7 +4377,7 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
@@ -4305,17 +4385,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS20" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
@@ -4417,12 +4502,12 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1990-10-01</t>
+          <t>1990-09-01</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>1990-10</t>
+          <t>1990-09</t>
         </is>
       </c>
       <c r="N21" t="n">
@@ -4531,7 +4616,7 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
@@ -4539,17 +4624,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS21" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
@@ -4651,12 +4741,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>1990-11-01</t>
+          <t>1990-10-01</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>1990-11</t>
+          <t>1990-10</t>
         </is>
       </c>
       <c r="N22" t="n">
@@ -4687,7 +4777,7 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
@@ -4695,17 +4785,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS22" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
@@ -4807,12 +4902,12 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1990-11-01</t>
+          <t>1990-10-01</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>1990-11</t>
+          <t>1990-10</t>
         </is>
       </c>
       <c r="N23" t="n">
@@ -4921,7 +5016,7 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
@@ -4929,17 +5024,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS23" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
@@ -5041,12 +5141,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1990-12-01</t>
+          <t>1990-11-01</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>1990-12</t>
+          <t>1990-11</t>
         </is>
       </c>
       <c r="N24" t="n">
@@ -5077,7 +5177,7 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ24" t="inlineStr">
@@ -5085,17 +5185,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS24" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV24" t="inlineStr">
@@ -5197,12 +5302,12 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1990-12-01</t>
+          <t>1990-11-01</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>1990-12</t>
+          <t>1990-11</t>
         </is>
       </c>
       <c r="N25" t="n">
@@ -5311,7 +5416,7 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ25" t="inlineStr">
@@ -5319,17 +5424,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS25" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV25" t="inlineStr">
@@ -5431,12 +5541,12 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1991-01-01</t>
+          <t>1990-12-01</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>1991-01</t>
+          <t>1990-12</t>
         </is>
       </c>
       <c r="N26" t="n">
@@ -5467,7 +5577,7 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ26" t="inlineStr">
@@ -5475,17 +5585,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS26" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV26" t="inlineStr">
@@ -5587,12 +5702,12 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>1991-01-01</t>
+          <t>1990-12-01</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>1991-01</t>
+          <t>1990-12</t>
         </is>
       </c>
       <c r="N27" t="n">
@@ -5701,7 +5816,7 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ27" t="inlineStr">
@@ -5709,17 +5824,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS27" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
@@ -5791,12 +5911,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -5821,19 +5941,19 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>1991-02-01</t>
+          <t>1991-01-01</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>1991-02</t>
+          <t>1991-01</t>
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -5842,12 +5962,12 @@
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D13_ANNUAL</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -5867,7 +5987,7 @@
       </c>
       <c r="AS28" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D13_ANNUAL</t>
         </is>
       </c>
       <c r="AT28" t="n">
@@ -5880,42 +6000,42 @@
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -5947,12 +6067,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -5977,38 +6097,38 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1991-02-01</t>
+          <t>1991-01-01</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>1991-02</t>
+          <t>1991-01</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D13_ANNUAL</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D13_ANNUAL</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_CA_PHAC_CNDSS</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Botulisme</t>
+          <t>Botulism</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -6018,12 +6138,12 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -6033,7 +6153,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:CA:national</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -6068,17 +6188,17 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -6101,7 +6221,7 @@
       </c>
       <c r="AS29" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D13_ANNUAL</t>
         </is>
       </c>
       <c r="AT29" t="n">
@@ -6114,42 +6234,42 @@
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6331,12 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1991-03-01</t>
+          <t>1991-01-01</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>1991-03</t>
+          <t>1991-01</t>
         </is>
       </c>
       <c r="N30" t="n">
@@ -6247,7 +6367,7 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ30" t="inlineStr">
@@ -6255,17 +6375,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS30" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV30" t="inlineStr">
@@ -6367,12 +6492,12 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>1991-03-01</t>
+          <t>1991-01-01</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>1991-03</t>
+          <t>1991-01</t>
         </is>
       </c>
       <c r="N31" t="n">
@@ -6481,7 +6606,7 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ31" t="inlineStr">
@@ -6489,17 +6614,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS31" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV31" t="inlineStr">
@@ -6601,12 +6731,12 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1991-04-01</t>
+          <t>1991-02-01</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>1991-04</t>
+          <t>1991-02</t>
         </is>
       </c>
       <c r="N32" t="n">
@@ -6637,7 +6767,7 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
@@ -6645,17 +6775,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS32" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
@@ -6757,12 +6892,12 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1991-04-01</t>
+          <t>1991-02-01</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>1991-04</t>
+          <t>1991-02</t>
         </is>
       </c>
       <c r="N33" t="n">
@@ -6871,7 +7006,7 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ33" t="inlineStr">
@@ -6879,17 +7014,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS33" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
@@ -6991,12 +7131,12 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>1991-05-01</t>
+          <t>1991-03-01</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>1991-05</t>
+          <t>1991-03</t>
         </is>
       </c>
       <c r="N34" t="n">
@@ -7027,7 +7167,7 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
@@ -7035,17 +7175,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS34" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
@@ -7147,12 +7292,12 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1991-05-01</t>
+          <t>1991-03-01</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>1991-05</t>
+          <t>1991-03</t>
         </is>
       </c>
       <c r="N35" t="n">
@@ -7261,7 +7406,7 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ35" t="inlineStr">
@@ -7269,17 +7414,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS35" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
@@ -7381,12 +7531,12 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>1991-06-01</t>
+          <t>1991-04-01</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>1991-06</t>
+          <t>1991-04</t>
         </is>
       </c>
       <c r="N36" t="n">
@@ -7417,7 +7567,7 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ36" t="inlineStr">
@@ -7425,17 +7575,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS36" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
@@ -7537,12 +7692,12 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1991-06-01</t>
+          <t>1991-04-01</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>1991-06</t>
+          <t>1991-04</t>
         </is>
       </c>
       <c r="N37" t="n">
@@ -7651,7 +7806,7 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ37" t="inlineStr">
@@ -7659,17 +7814,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS37" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
@@ -7771,12 +7931,12 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>1991-07-01</t>
+          <t>1991-05-01</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>1991-07</t>
+          <t>1991-05</t>
         </is>
       </c>
       <c r="N38" t="n">
@@ -7807,7 +7967,7 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ38" t="inlineStr">
@@ -7815,17 +7975,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS38" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV38" t="inlineStr">
@@ -7927,12 +8092,12 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>1991-07-01</t>
+          <t>1991-05-01</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>1991-07</t>
+          <t>1991-05</t>
         </is>
       </c>
       <c r="N39" t="n">
@@ -8041,7 +8206,7 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ39" t="inlineStr">
@@ -8049,17 +8214,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR39" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS39" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV39" t="inlineStr">
@@ -8161,12 +8331,12 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>1991-08-01</t>
+          <t>1991-06-01</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>1991-08</t>
+          <t>1991-06</t>
         </is>
       </c>
       <c r="N40" t="n">
@@ -8197,7 +8367,7 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ40" t="inlineStr">
@@ -8205,17 +8375,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR40" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS40" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV40" t="inlineStr">
@@ -8317,12 +8492,12 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>1991-08-01</t>
+          <t>1991-06-01</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>1991-08</t>
+          <t>1991-06</t>
         </is>
       </c>
       <c r="N41" t="n">
@@ -8431,7 +8606,7 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ41" t="inlineStr">
@@ -8439,17 +8614,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR41" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS41" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV41" t="inlineStr">
@@ -8551,12 +8731,12 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>1991-09-01</t>
+          <t>1991-07-01</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>1991-09</t>
+          <t>1991-07</t>
         </is>
       </c>
       <c r="N42" t="n">
@@ -8587,7 +8767,7 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ42" t="inlineStr">
@@ -8595,17 +8775,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR42" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS42" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV42" t="inlineStr">
@@ -8707,12 +8892,12 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>1991-09-01</t>
+          <t>1991-07-01</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>1991-09</t>
+          <t>1991-07</t>
         </is>
       </c>
       <c r="N43" t="n">
@@ -8821,7 +9006,7 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ43" t="inlineStr">
@@ -8829,17 +9014,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS43" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV43" t="inlineStr">
@@ -8941,12 +9131,12 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>1991-10-01</t>
+          <t>1991-08-01</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>1991-10</t>
+          <t>1991-08</t>
         </is>
       </c>
       <c r="N44" t="n">
@@ -8977,7 +9167,7 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ44" t="inlineStr">
@@ -8985,17 +9175,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR44" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS44" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV44" t="inlineStr">
@@ -9097,12 +9292,12 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>1991-10-01</t>
+          <t>1991-08-01</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>1991-10</t>
+          <t>1991-08</t>
         </is>
       </c>
       <c r="N45" t="n">
@@ -9211,7 +9406,7 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ45" t="inlineStr">
@@ -9219,17 +9414,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR45" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS45" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV45" t="inlineStr">
@@ -9331,12 +9531,12 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>1991-11-01</t>
+          <t>1991-09-01</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>1991-11</t>
+          <t>1991-09</t>
         </is>
       </c>
       <c r="N46" t="n">
@@ -9367,7 +9567,7 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ46" t="inlineStr">
@@ -9375,17 +9575,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS46" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
@@ -9487,12 +9692,12 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>1991-11-01</t>
+          <t>1991-09-01</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>1991-11</t>
+          <t>1991-09</t>
         </is>
       </c>
       <c r="N47" t="n">
@@ -9601,7 +9806,7 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ47" t="inlineStr">
@@ -9609,17 +9814,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS47" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV47" t="inlineStr">
@@ -9721,61 +9931,66 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>1991-12-01</t>
+          <t>1991-10-01</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>1991-12</t>
+          <t>1991-10</t>
         </is>
       </c>
       <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_307_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP48" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ48" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS48" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_307_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT48" t="n">
         <v>2</v>
       </c>
-      <c r="O48" t="n">
-        <v>2</v>
-      </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP48" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ48" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS48" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT48" t="n">
-        <v>1</v>
-      </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV48" t="inlineStr">
@@ -9877,19 +10092,19 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>1991-12-01</t>
+          <t>1991-10-01</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>1991-12</t>
+          <t>1991-10</t>
         </is>
       </c>
       <c r="N49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U49" t="inlineStr">
         <is>
@@ -9991,7 +10206,7 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ49" t="inlineStr">
@@ -9999,17 +10214,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS49" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV49" t="inlineStr">
@@ -10111,12 +10331,12 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>1994-01-01</t>
+          <t>1991-11-01</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>1994-01</t>
+          <t>1991-11</t>
         </is>
       </c>
       <c r="N50" t="n">
@@ -10147,7 +10367,7 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ50" t="inlineStr">
@@ -10155,17 +10375,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR50" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS50" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV50" t="inlineStr">
@@ -10267,12 +10492,12 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>1994-01-01</t>
+          <t>1991-11-01</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>1994-01</t>
+          <t>1991-11</t>
         </is>
       </c>
       <c r="N51" t="n">
@@ -10381,7 +10606,7 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ51" t="inlineStr">
@@ -10389,17 +10614,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS51" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV51" t="inlineStr">
@@ -10501,19 +10731,19 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>1994-02-01</t>
+          <t>1991-12-01</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>1994-02</t>
+          <t>1991-12</t>
         </is>
       </c>
       <c r="N52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -10537,7 +10767,7 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ52" t="inlineStr">
@@ -10545,17 +10775,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR52" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS52" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV52" t="inlineStr">
@@ -10657,19 +10892,19 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>1994-02-01</t>
+          <t>1991-12-01</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>1994-02</t>
+          <t>1991-12</t>
         </is>
       </c>
       <c r="N53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U53" t="inlineStr">
         <is>
@@ -10771,7 +11006,7 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ53" t="inlineStr">
@@ -10779,17 +11014,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS53" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV53" t="inlineStr">
@@ -10861,12 +11101,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -10891,19 +11131,19 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>1994-03-01</t>
+          <t>1992-01-01</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>1994-03</t>
+          <t>1992-01</t>
         </is>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -10912,12 +11152,12 @@
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D13_ANNUAL</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
@@ -10937,7 +11177,7 @@
       </c>
       <c r="AS54" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D13_ANNUAL</t>
         </is>
       </c>
       <c r="AT54" t="n">
@@ -10950,42 +11190,42 @@
       </c>
       <c r="AV54" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC54" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -11017,12 +11257,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -11047,38 +11287,38 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>1994-03-01</t>
+          <t>1992-01-01</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>1994-03</t>
+          <t>1992-01</t>
         </is>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D13_ANNUAL</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D13_ANNUAL</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_CA_PHAC_CNDSS</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Botulisme</t>
+          <t>Botulism</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
@@ -11088,12 +11328,12 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
@@ -11103,7 +11343,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:CA:national</t>
         </is>
       </c>
       <c r="AD55" t="inlineStr">
@@ -11138,17 +11378,17 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
         </is>
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -11171,7 +11411,7 @@
       </c>
       <c r="AS55" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D13_ANNUAL</t>
         </is>
       </c>
       <c r="AT55" t="n">
@@ -11184,42 +11424,42 @@
       </c>
       <c r="AV55" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC55" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -11251,12 +11491,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -11281,19 +11521,19 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>1994-04-01</t>
+          <t>1993-01-01</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>1994-04</t>
+          <t>1993-01</t>
         </is>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -11302,12 +11542,12 @@
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D13_ANNUAL</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
@@ -11327,7 +11567,7 @@
       </c>
       <c r="AS56" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D13_ANNUAL</t>
         </is>
       </c>
       <c r="AT56" t="n">
@@ -11340,42 +11580,42 @@
       </c>
       <c r="AV56" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC56" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -11407,12 +11647,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -11437,38 +11677,38 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>1994-04-01</t>
+          <t>1993-01-01</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>1994-04</t>
+          <t>1993-01</t>
         </is>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D13_ANNUAL</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D13_ANNUAL</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_CA_PHAC_CNDSS</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>Botulisme</t>
+          <t>Botulism</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
@@ -11478,12 +11718,12 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
@@ -11493,7 +11733,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:CA:national</t>
         </is>
       </c>
       <c r="AD57" t="inlineStr">
@@ -11528,17 +11768,17 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
         </is>
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -11561,7 +11801,7 @@
       </c>
       <c r="AS57" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D13_ANNUAL</t>
         </is>
       </c>
       <c r="AT57" t="n">
@@ -11574,42 +11814,42 @@
       </c>
       <c r="AV57" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB57" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC57" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -11641,12 +11881,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -11671,19 +11911,19 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>1994-05-01</t>
+          <t>1994-01-01</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>1994-05</t>
+          <t>1994-01</t>
         </is>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -11692,12 +11932,12 @@
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D13_ANNUAL</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
@@ -11717,7 +11957,7 @@
       </c>
       <c r="AS58" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D13_ANNUAL</t>
         </is>
       </c>
       <c r="AT58" t="n">
@@ -11730,42 +11970,42 @@
       </c>
       <c r="AV58" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC58" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -11797,12 +12037,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -11827,38 +12067,38 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>1994-05-01</t>
+          <t>1994-01-01</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>1994-05</t>
+          <t>1994-01</t>
         </is>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D13_ANNUAL</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D13_ANNUAL</t>
         </is>
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_CA_PHAC_CNDSS</t>
         </is>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Botulisme</t>
+          <t>Botulism</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
@@ -11868,12 +12108,12 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
@@ -11883,7 +12123,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:CA:national</t>
         </is>
       </c>
       <c r="AD59" t="inlineStr">
@@ -11918,17 +12158,17 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
         </is>
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -11951,7 +12191,7 @@
       </c>
       <c r="AS59" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D13_ANNUAL</t>
         </is>
       </c>
       <c r="AT59" t="n">
@@ -11964,42 +12204,42 @@
       </c>
       <c r="AV59" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB59" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC59" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -12061,12 +12301,12 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>1994-06-01</t>
+          <t>1994-01-01</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>1994-06</t>
+          <t>1994-01</t>
         </is>
       </c>
       <c r="N60" t="n">
@@ -12097,7 +12337,7 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ60" t="inlineStr">
@@ -12105,17 +12345,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR60" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS60" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV60" t="inlineStr">
@@ -12217,12 +12462,12 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>1994-06-01</t>
+          <t>1994-01-01</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>1994-06</t>
+          <t>1994-01</t>
         </is>
       </c>
       <c r="N61" t="n">
@@ -12331,7 +12576,7 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ61" t="inlineStr">
@@ -12339,17 +12584,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR61" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS61" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV61" t="inlineStr">
@@ -12451,19 +12701,19 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>1994-07-01</t>
+          <t>1994-02-01</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>1994-07</t>
+          <t>1994-02</t>
         </is>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -12487,7 +12737,7 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ62" t="inlineStr">
@@ -12495,17 +12745,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR62" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS62" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV62" t="inlineStr">
@@ -12607,19 +12862,19 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>1994-07-01</t>
+          <t>1994-02-01</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>1994-07</t>
+          <t>1994-02</t>
         </is>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>
@@ -12721,7 +12976,7 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ63" t="inlineStr">
@@ -12729,17 +12984,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR63" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS63" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV63" t="inlineStr">
@@ -12841,12 +13101,12 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>1994-08-01</t>
+          <t>1994-03-01</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>1994-08</t>
+          <t>1994-03</t>
         </is>
       </c>
       <c r="N64" t="n">
@@ -12877,7 +13137,7 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ64" t="inlineStr">
@@ -12885,17 +13145,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR64" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS64" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV64" t="inlineStr">
@@ -12997,12 +13262,12 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>1994-08-01</t>
+          <t>1994-03-01</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>1994-08</t>
+          <t>1994-03</t>
         </is>
       </c>
       <c r="N65" t="n">
@@ -13111,7 +13376,7 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ65" t="inlineStr">
@@ -13119,17 +13384,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR65" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS65" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV65" t="inlineStr">
@@ -13231,12 +13501,12 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>1994-09-01</t>
+          <t>1994-04-01</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>1994-09</t>
+          <t>1994-04</t>
         </is>
       </c>
       <c r="N66" t="n">
@@ -13267,7 +13537,7 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ66" t="inlineStr">
@@ -13275,17 +13545,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR66" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS66" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV66" t="inlineStr">
@@ -13387,12 +13662,12 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>1994-09-01</t>
+          <t>1994-04-01</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>1994-09</t>
+          <t>1994-04</t>
         </is>
       </c>
       <c r="N67" t="n">
@@ -13501,7 +13776,7 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ67" t="inlineStr">
@@ -13509,17 +13784,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR67" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS67" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV67" t="inlineStr">
@@ -13621,12 +13901,12 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>1994-10-01</t>
+          <t>1994-05-01</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>1994-10</t>
+          <t>1994-05</t>
         </is>
       </c>
       <c r="N68" t="n">
@@ -13657,7 +13937,7 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ68" t="inlineStr">
@@ -13665,17 +13945,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR68" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS68" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV68" t="inlineStr">
@@ -13777,12 +14062,12 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>1994-10-01</t>
+          <t>1994-05-01</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>1994-10</t>
+          <t>1994-05</t>
         </is>
       </c>
       <c r="N69" t="n">
@@ -13891,7 +14176,7 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ69" t="inlineStr">
@@ -13899,17 +14184,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR69" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS69" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV69" t="inlineStr">
@@ -14011,12 +14301,12 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>1994-11-01</t>
+          <t>1994-06-01</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>1994-11</t>
+          <t>1994-06</t>
         </is>
       </c>
       <c r="N70" t="n">
@@ -14047,7 +14337,7 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ70" t="inlineStr">
@@ -14055,17 +14345,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR70" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS70" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV70" t="inlineStr">
@@ -14167,12 +14462,12 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>1994-11-01</t>
+          <t>1994-06-01</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>1994-11</t>
+          <t>1994-06</t>
         </is>
       </c>
       <c r="N71" t="n">
@@ -14281,7 +14576,7 @@
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ71" t="inlineStr">
@@ -14289,17 +14584,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR71" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS71" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV71" t="inlineStr">
@@ -14401,12 +14701,12 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>1994-12-01</t>
+          <t>1994-07-01</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>1994-12</t>
+          <t>1994-07</t>
         </is>
       </c>
       <c r="N72" t="n">
@@ -14437,7 +14737,7 @@
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ72" t="inlineStr">
@@ -14445,17 +14745,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR72" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS72" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV72" t="inlineStr">
@@ -14557,12 +14862,12 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>1994-12-01</t>
+          <t>1994-07-01</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>1994-12</t>
+          <t>1994-07</t>
         </is>
       </c>
       <c r="N73" t="n">
@@ -14671,7 +14976,7 @@
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ73" t="inlineStr">
@@ -14679,55 +14984,2060 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR73" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS73" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT73" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV73" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA73" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB73" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC73" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>botulism</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>肉毒杆菌中毒</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>1994-08-01</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>1994-08</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_307_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP74" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ74" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR74" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS74" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_307_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT74" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV74" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA74" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB74" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC74" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>botulism</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>肉毒杆菌中毒</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>1994-08-01</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>1994-08</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_307_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_307_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>Botulisme</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD75" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE75" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF75" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG75" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM75" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN75" t="b">
         <v>1</v>
       </c>
-      <c r="AU73" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV73" t="inlineStr">
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP75" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ75" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR75" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS75" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_307_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV75" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW73" t="inlineStr">
+      <c r="AW75" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
+      <c r="AX75" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY73" t="inlineStr">
+      <c r="AY75" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ73" t="inlineStr">
+      <c r="AZ75" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA73" t="inlineStr">
+      <c r="BA75" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB73" t="inlineStr">
+      <c r="BB75" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC73" t="inlineStr">
+      <c r="BC75" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>botulism</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>肉毒杆菌中毒</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>1994-09-01</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>1994-09</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_307_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP76" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ76" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR76" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS76" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_307_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT76" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV76" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA76" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB76" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC76" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>botulism</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>肉毒杆菌中毒</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>1994-09-01</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>1994-09</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_307_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_307_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>Botulisme</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD77" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE77" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF77" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG77" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN77" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP77" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ77" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR77" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS77" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_307_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT77" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV77" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA77" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB77" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC77" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>botulism</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>肉毒杆菌中毒</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>1994-10-01</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>1994-10</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_307_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP78" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ78" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR78" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS78" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_307_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT78" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV78" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA78" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB78" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC78" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>botulism</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>肉毒杆菌中毒</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>1994-10-01</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>1994-10</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_307_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_307_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>Botulisme</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD79" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE79" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF79" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG79" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM79" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN79" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP79" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ79" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR79" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS79" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_307_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT79" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV79" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA79" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB79" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC79" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>botulism</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>肉毒杆菌中毒</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>1994-11-01</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>1994-11</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_307_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP80" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ80" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR80" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS80" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_307_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT80" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV80" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA80" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB80" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC80" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>botulism</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>肉毒杆菌中毒</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>1994-11-01</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>1994-11</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_307_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_307_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>Botulisme</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD81" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE81" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF81" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG81" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN81" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP81" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ81" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR81" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS81" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_307_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT81" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV81" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA81" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB81" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC81" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>botulism</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>肉毒杆菌中毒</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>1994-12-01</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>1994-12</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_307_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP82" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ82" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR82" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS82" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_307_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT82" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV82" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA82" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB82" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC82" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>botulism</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>肉毒杆菌中毒</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>1994-12-01</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>1994-12</t>
+        </is>
+      </c>
+      <c r="N83" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0</v>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_307_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_307_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>Botulisme</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD83" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE83" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF83" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG83" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN83" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP83" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ83" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR83" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS83" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_307_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT83" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV83" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA83" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB83" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC83" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -14849,7 +17159,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10">
@@ -14859,7 +17169,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11">
@@ -14879,7 +17189,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13">
@@ -14889,7 +17199,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -14911,7 +17221,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
